--- a/geocoded_cache_healthy.xlsx
+++ b/geocoded_cache_healthy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,163 @@
         <v>127.112688386546</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>수동 
+1등</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>37.7427114349339</v>
+      </c>
+      <c r="C11" t="n">
+        <v>127.296206187177</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>부산 금정구</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>35.2427772019609</v>
+      </c>
+      <c r="C12" t="n">
+        <v>129.092095292484</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>광주 서구</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>35.1520722691295</v>
+      </c>
+      <c r="C13" t="n">
+        <v>126.890187526298</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>울산 동구</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>35.5046358750559</v>
+      </c>
+      <c r="C14" t="n">
+        <v>129.416487775873</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>경기 화성시</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>37.1995372034717</v>
+      </c>
+      <c r="C15" t="n">
+        <v>126.831477350333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>경기 포천시</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>37.8949928340087</v>
+      </c>
+      <c r="C16" t="n">
+        <v>127.200332890652</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>경기 시흥시</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>37.3801150715958</v>
+      </c>
+      <c r="C17" t="n">
+        <v>126.802977796436</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>35.228565355864</v>
+      </c>
+      <c r="C18" t="n">
+        <v>128.88936269803</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>경북 고령군</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>35.7260653208402</v>
+      </c>
+      <c r="C19" t="n">
+        <v>128.262895757558</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>제주 서귀포시</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>33.2540646255023</v>
+      </c>
+      <c r="C20" t="n">
+        <v>126.559563466911</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>전남 영암군</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>34.8000591144732</v>
+      </c>
+      <c r="C21" t="n">
+        <v>126.696762590551</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>강원 춘천시</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>37.8812440340087</v>
+      </c>
+      <c r="C22" t="n">
+        <v>127.730207024668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geocoded_cache_healthy.xlsx
+++ b/geocoded_cache_healthy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,279 @@
         <v>127.730207024668</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>서울 은평구</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>37.6028174370821</v>
+      </c>
+      <c r="C23" t="n">
+        <v>126.928940981464</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>수동</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>37.7034248082825</v>
+      </c>
+      <c r="C24" t="n">
+        <v>127.325841809387</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>서울 노원구 동일로 1308 정안프라자 102호 일부</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>37.6459751467144</v>
+      </c>
+      <c r="C25" t="n">
+        <v>127.064166413458</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>인천 남동구 남동대로765번길 26</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>37.4510577012885</v>
+      </c>
+      <c r="C26" t="n">
+        <v>126.706219577999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>울산 남구 수암로 21</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>35.5319541900421</v>
+      </c>
+      <c r="C27" t="n">
+        <v>129.310571822079</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>경기 부천시 부일로221번길 26 삼원타운1층-120</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>37.4895114497717</v>
+      </c>
+      <c r="C28" t="n">
+        <v>126.755112180136</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>경기 의정부시 신흥로 93</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>37.7244361083853</v>
+      </c>
+      <c r="C29" t="n">
+        <v>127.043559498608</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>경기 성남시 분당구 황새울로360번길 35 2층 231호</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>37.384910507805</v>
+      </c>
+      <c r="C30" t="n">
+        <v>127.124672146785</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>경기 이천시 사동로 128 복권방</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>37.2402984268252</v>
+      </c>
+      <c r="C31" t="n">
+        <v>127.496468099962</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>경기 양평군 신내길7번길 48 1층 세븐일레븐</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>37.4683575128184</v>
+      </c>
+      <c r="C32" t="n">
+        <v>127.532035862391</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>충북 청주시 청원구 중심상업로 47 103호</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>36.7150765562734</v>
+      </c>
+      <c r="C33" t="n">
+        <v>127.428954460961</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>경북 구미시 문장로25길 7 GS25구미원호점</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>36.1514753162037</v>
+      </c>
+      <c r="C34" t="n">
+        <v>128.329243128009</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>경남 창원시 마산합포구 신서촌1길 49</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>35.116007672958</v>
+      </c>
+      <c r="C35" t="n">
+        <v>128.486403876131</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>인천 부평구</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>37.5070416636401</v>
+      </c>
+      <c r="C36" t="n">
+        <v>126.721864167603</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>광주 북구</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>35.1741733740375</v>
+      </c>
+      <c r="C37" t="n">
+        <v>126.912012078919</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>대전 서구</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>36.3554987200538</v>
+      </c>
+      <c r="C38" t="n">
+        <v>127.383789715873</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>대전 동구</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>36.3117768357127</v>
+      </c>
+      <c r="C39" t="n">
+        <v>127.454807132217</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>경기 파주시</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>37.7600449967302</v>
+      </c>
+      <c r="C40" t="n">
+        <v>126.779881359268</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>경기 의정부시</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>37.7380566430616</v>
+      </c>
+      <c r="C41" t="n">
+        <v>127.033899090337</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>경기 부천시</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>37.5035117792841</v>
+      </c>
+      <c r="C42" t="n">
+        <v>126.766038450927</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>경남 거제시</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>34.8805390453822</v>
+      </c>
+      <c r="C43" t="n">
+        <v>128.621129462965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
